--- a/data/trans_orig/P19E-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19E-Clase-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que se cepilla los dientes al día en 2016</t>
+          <t>Población según el número de veces que se cepilla los dientes al día en 2016 (tasa de respuesta: 97,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>183523</t>
+          <t>182800</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>226681</t>
+          <t>225070</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>190682</t>
+          <t>188846</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>225899</t>
+          <t>227364</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>385362</t>
+          <t>386507</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>444098</t>
+          <t>445102</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,04%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94501</t>
+          <t>94545</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130451</t>
+          <t>131716</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73871</t>
+          <t>71593</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>107185</t>
+          <t>105357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>176789</t>
+          <t>175204</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>225992</t>
+          <t>226176</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,49%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69993</t>
+          <t>70482</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105685</t>
+          <t>106412</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31853</t>
+          <t>33010</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56590</t>
+          <t>57060</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>110700</t>
+          <t>108795</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>154880</t>
+          <t>153854</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20846</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5669</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20520</t>
+          <t>21376</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15261</t>
+          <t>15499</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,82 +1198,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4098</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1156</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>10504</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>11226</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>5114</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>20365</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>0,67%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>4098</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>989</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>9748</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>11226</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>5269</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>20497</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>144205</t>
+          <t>143053</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>184557</t>
+          <t>181998</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>163912</t>
+          <t>162685</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>202905</t>
+          <t>201327</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>320678</t>
+          <t>318561</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>375266</t>
+          <t>374552</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,0%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97191</t>
+          <t>98753</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>133148</t>
+          <t>134126</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>106437</t>
+          <t>106179</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142638</t>
+          <t>142459</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>213570</t>
+          <t>215612</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>265925</t>
+          <t>269500</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,7%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52972</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82607</t>
+          <t>85305</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42921</t>
+          <t>43116</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71461</t>
+          <t>72372</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>102105</t>
+          <t>103483</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>143407</t>
+          <t>145840</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12972</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11339</t>
+          <t>10466</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17734</t>
+          <t>18086</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9026</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25167</t>
+          <t>24501</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8726</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25771</t>
+          <t>25161</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>152897</t>
+          <t>151559</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>197004</t>
+          <t>194710</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>68508</t>
+          <t>67507</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94909</t>
+          <t>94417</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>228736</t>
+          <t>229395</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>279350</t>
+          <t>281887</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,91%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>139210</t>
+          <t>136622</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>181108</t>
+          <t>179670</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38415</t>
+          <t>38964</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63261</t>
+          <t>62160</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>184920</t>
+          <t>182774</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>231530</t>
+          <t>232232</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,53%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>112748</t>
+          <t>113557</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>151137</t>
+          <t>154056</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16476</t>
+          <t>16195</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35046</t>
+          <t>35197</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>134283</t>
+          <t>134154</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>178693</t>
+          <t>178895</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16806</t>
+          <t>17021</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,82 +2449,82 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>3841</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1239</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>10118</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>6,21%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>12801</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>6475</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>22216</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>3,3%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3841</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1229</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>10463</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>12801</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>6524</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>22320</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27167</t>
+          <t>28093</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52264</t>
+          <t>52724</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>12114</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29740</t>
+          <t>29586</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>56553</t>
+          <t>55480</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>313969</t>
+          <t>313069</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>376401</t>
+          <t>374560</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>323054</t>
+          <t>318625</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>377687</t>
+          <t>379363</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>649619</t>
+          <t>651035</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>730480</t>
+          <t>737554</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>300387</t>
+          <t>299467</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>361097</t>
+          <t>359287</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>272338</t>
+          <t>269102</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>324822</t>
+          <t>327923</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>590458</t>
+          <t>587505</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>670502</t>
+          <t>667828</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>270040</t>
+          <t>269159</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>330866</t>
+          <t>329380</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>112864</t>
+          <t>112018</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155030</t>
+          <t>155929</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>399249</t>
+          <t>397919</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>472579</t>
+          <t>470379</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27366</t>
+          <t>25692</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49981</t>
+          <t>51111</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,82 +3131,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>4269</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>19555</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>47222</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>34669</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>65153</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>2,46%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>9724</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>4357</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>19216</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>47222</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>35004</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>63892</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>83267</t>
+          <t>85404</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>123529</t>
+          <t>123754</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7727</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23930</t>
+          <t>23480</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>96736</t>
+          <t>95599</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>139722</t>
+          <t>138750</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>133176</t>
+          <t>134072</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178527</t>
+          <t>176432</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>234625</t>
+          <t>233009</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>287099</t>
+          <t>285677</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>380562</t>
+          <t>380866</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>447792</t>
+          <t>450167</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>160888</t>
+          <t>160672</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>205266</t>
+          <t>204823</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>220740</t>
+          <t>221176</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>272485</t>
+          <t>271352</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>393282</t>
+          <t>391591</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>460644</t>
+          <t>461919</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>136891</t>
+          <t>138780</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>182314</t>
+          <t>181134</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>146849</t>
+          <t>142515</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>191422</t>
+          <t>189271</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>294085</t>
+          <t>292116</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>355947</t>
+          <t>354464</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20008</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41907</t>
+          <t>42339</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7506</t>
+          <t>7334</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>22664</t>
+          <t>23099</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>31644</t>
+          <t>31624</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>56851</t>
+          <t>56695</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>59537</t>
+          <t>59476</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>92456</t>
+          <t>92908</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>26248</t>
+          <t>27325</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>53002</t>
+          <t>51135</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>93287</t>
+          <t>94368</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>135368</t>
+          <t>135493</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>99108</t>
+          <t>99629</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>131886</t>
+          <t>131628</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>374215</t>
+          <t>376151</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>441064</t>
+          <t>440621</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>485719</t>
+          <t>487653</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>559943</t>
+          <t>561241</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,51%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>80453</t>
+          <t>79278</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>112084</t>
+          <t>110562</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>291827</t>
+          <t>289643</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>350664</t>
+          <t>350283</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>383804</t>
+          <t>381610</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>451098</t>
+          <t>450958</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>47798</t>
+          <t>48816</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>77251</t>
+          <t>77058</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>188846</t>
+          <t>187484</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>241346</t>
+          <t>243809</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>246066</t>
+          <t>246471</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>306756</t>
+          <t>307119</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>11079</t>
+          <t>10703</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>22925</t>
+          <t>22356</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>47735</t>
+          <t>47020</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>26074</t>
+          <t>26475</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>54232</t>
+          <t>51695</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>9705</t>
+          <t>9456</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>48404</t>
+          <t>48129</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>80793</t>
+          <t>83382</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>51520</t>
+          <t>50965</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>83231</t>
+          <t>83887</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1102825</t>
+          <t>1093801</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1208304</t>
+          <t>1211987</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1429658</t>
+          <t>1430088</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1556513</t>
+          <t>1548114</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2556243</t>
+          <t>2566187</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2722707</t>
+          <t>2728875</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>940926</t>
+          <t>936230</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1044974</t>
+          <t>1041700</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1071708</t>
+          <t>1071914</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1183603</t>
+          <t>1187456</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2042381</t>
+          <t>2043988</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2204309</t>
+          <t>2199923</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>760481</t>
+          <t>754543</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>857471</t>
+          <t>860129</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>592017</t>
+          <t>589397</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>682771</t>
+          <t>684090</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1377414</t>
+          <t>1376292</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1515374</t>
+          <t>1506111</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>80550</t>
+          <t>81039</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>119656</t>
+          <t>120515</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>47301</t>
+          <t>48038</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>81661</t>
+          <t>83103</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>136942</t>
+          <t>138411</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>190758</t>
+          <t>190152</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>213255</t>
+          <t>211167</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>272804</t>
+          <t>275175</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>103101</t>
+          <t>102842</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>149617</t>
+          <t>147709</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>330400</t>
+          <t>328371</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>402891</t>
+          <t>404033</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que se cepilla los dientes al día en 2023</t>
+          <t>Población según el número de veces que se cepilla los dientes al día en 2023 (tasa de respuesta: 99,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>125762</t>
+          <t>126621</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>166855</t>
+          <t>167065</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>185026</t>
+          <t>184733</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>221457</t>
+          <t>221130</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>322749</t>
+          <t>319997</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>377790</t>
+          <t>377176</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,65%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>254492</t>
+          <t>252061</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>298394</t>
+          <t>297559</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>189800</t>
+          <t>188630</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>226088</t>
+          <t>224319</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>454528</t>
+          <t>452805</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>512427</t>
+          <t>511632</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,78%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62925</t>
+          <t>64141</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>96028</t>
+          <t>100520</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24179</t>
+          <t>24954</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44754</t>
+          <t>46334</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>94262</t>
+          <t>93306</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>131750</t>
+          <t>132969</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6280</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>561</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1391</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8588</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6588</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6705</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>9686</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103163</t>
+          <t>102821</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>141124</t>
+          <t>141880</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>134758</t>
+          <t>135290</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>167783</t>
+          <t>167243</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>248337</t>
+          <t>246687</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>298861</t>
+          <t>300029</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,99%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>209521</t>
+          <t>208158</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>253954</t>
+          <t>253254</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>172946</t>
+          <t>173807</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>204065</t>
+          <t>206132</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>393599</t>
+          <t>393433</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>447711</t>
+          <t>447636</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,69%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68611</t>
+          <t>67025</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103073</t>
+          <t>101941</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31054</t>
+          <t>30695</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50926</t>
+          <t>50153</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>104502</t>
+          <t>103882</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>146572</t>
+          <t>144979</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>11084</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13618</t>
+          <t>12654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18417</t>
+          <t>16527</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>574</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18899</t>
+          <t>18839</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>112357</t>
+          <t>114962</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>546399</t>
+          <t>529590</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39815</t>
+          <t>40400</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59554</t>
+          <t>59975</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>171021</t>
+          <t>170252</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>644326</t>
+          <t>631511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>75,98%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74246</t>
+          <t>85917</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>357855</t>
+          <t>360216</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>82444</t>
+          <t>82188</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103324</t>
+          <t>101777</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>128104</t>
+          <t>136602</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>453281</t>
+          <t>453319</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33463</t>
+          <t>36863</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>162141</t>
+          <t>160226</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16020</t>
+          <t>15640</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28719</t>
+          <t>28735</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46199</t>
+          <t>49391</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>175002</t>
+          <t>178426</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>972</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>13576</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>287</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13943</t>
+          <t>13661</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33934</t>
+          <t>34075</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>526</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>8134</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34178</t>
+          <t>36128</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>163658</t>
+          <t>163196</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>224479</t>
+          <t>218076</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>126779</t>
+          <t>121759</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>318612</t>
+          <t>317486</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>295092</t>
+          <t>294902</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>500030</t>
+          <t>497748</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7898,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>476462</t>
+          <t>473227</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>549152</t>
+          <t>547982</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7933,12 +7933,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>526277</t>
+          <t>527515</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>802119</t>
+          <t>792385</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1029783</t>
+          <t>1029094</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1399931</t>
+          <t>1444891</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7983,12 +7983,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>72,07%</t>
         </is>
       </c>
     </row>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>231950</t>
+          <t>230212</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>295371</t>
+          <t>294112</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8026,12 +8026,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>43279</t>
+          <t>43075</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>116888</t>
+          <t>113788</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>246462</t>
+          <t>245489</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>397024</t>
+          <t>406518</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -8124,12 +8124,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12373</t>
+          <t>12215</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29183</t>
+          <t>27781</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8139,12 +8139,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8159,12 +8159,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12956</t>
+          <t>12535</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8194,12 +8194,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16460</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35918</t>
+          <t>36533</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -8237,12 +8237,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31140</t>
+          <t>31417</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>56861</t>
+          <t>58172</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8252,12 +8252,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8272,12 +8272,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18878</t>
+          <t>18624</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8287,12 +8287,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8307,12 +8307,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>36550</t>
+          <t>37034</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>69767</t>
+          <t>72502</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>62122</t>
+          <t>63923</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>104235</t>
+          <t>105729</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>157516</t>
+          <t>159780</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>274929</t>
+          <t>280298</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>237420</t>
+          <t>238863</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>367693</t>
+          <t>372867</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +8580,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>200617</t>
+          <t>203012</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>247879</t>
+          <t>247423</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8615,12 +8615,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>389907</t>
+          <t>386239</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>539046</t>
+          <t>537595</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>608727</t>
+          <t>610949</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>773582</t>
+          <t>770088</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8665,12 +8665,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>58,87%</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8693,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>103798</t>
+          <t>106168</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>145148</t>
+          <t>143682</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>108176</t>
+          <t>105428</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>170416</t>
+          <t>168498</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8743,12 +8743,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>218375</t>
+          <t>220995</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>300580</t>
+          <t>297634</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8616</t>
+          <t>8527</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22339</t>
+          <t>21773</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21234</t>
+          <t>21723</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8856,12 +8856,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>20023</t>
+          <t>20687</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>38999</t>
+          <t>39704</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8891,12 +8891,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -8919,12 +8919,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>20985</t>
+          <t>21220</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>40811</t>
+          <t>41723</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8934,82 +8934,82 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>27904</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>19502</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>37700</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>58050</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>44032</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>72071</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
           <t>4,44%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>27904</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>20342</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>37941</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>58050</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>44739</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>72677</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>53366</t>
+          <t>55221</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>105150</t>
+          <t>103708</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>184956</t>
+          <t>184859</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>234950</t>
+          <t>235320</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>250701</t>
+          <t>251186</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>322217</t>
+          <t>324630</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,79%</t>
         </is>
       </c>
     </row>
@@ -9262,12 +9262,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>116129</t>
+          <t>118353</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>169208</t>
+          <t>168715</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9297,12 +9297,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>358939</t>
+          <t>358181</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>410015</t>
+          <t>408752</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9332,12 +9332,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>494716</t>
+          <t>491416</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>567213</t>
+          <t>567366</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9347,12 +9347,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,31%</t>
         </is>
       </c>
     </row>
@@ -9375,12 +9375,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7382</t>
+          <t>6569</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>31817</t>
+          <t>31069</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9410,12 +9410,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>100552</t>
+          <t>100387</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>132281</t>
+          <t>131734</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>115215</t>
+          <t>114528</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>152884</t>
+          <t>153780</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9523,12 +9523,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7466</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>18179</t>
+          <t>19088</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>19663</t>
+          <t>19935</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -9601,12 +9601,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9621,7 +9621,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9636,12 +9636,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>21514</t>
+          <t>21324</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>38362</t>
+          <t>39322</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>22516</t>
+          <t>22265</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>40620</t>
+          <t>40144</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -9831,12 +9831,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>734802</t>
+          <t>733173</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1477521</t>
+          <t>1471231</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9846,12 +9846,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9866,12 +9866,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>862319</t>
+          <t>858646</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1167318</t>
+          <t>1165970</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1769357</t>
+          <t>1779486</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2642963</t>
+          <t>2640085</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,16%</t>
         </is>
       </c>
     </row>
@@ -9944,12 +9944,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1263226</t>
+          <t>1249728</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1764053</t>
+          <t>1757217</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9959,12 +9959,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1804153</t>
+          <t>1805738</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2268866</t>
+          <t>2256375</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3181063</t>
+          <t>3158911</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3824280</t>
+          <t>3815954</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,15%</t>
         </is>
       </c>
     </row>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>520275</t>
+          <t>507819</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>732296</t>
+          <t>733565</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10072,12 +10072,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>355985</t>
+          <t>350933</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>484024</t>
+          <t>486873</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>947696</t>
+          <t>958621</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1190970</t>
+          <t>1196554</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -10170,12 +10170,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>34790</t>
+          <t>35170</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>62665</t>
+          <t>62002</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10185,12 +10185,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>28620</t>
+          <t>28547</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>48869</t>
+          <t>50391</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10225,7 +10225,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>69235</t>
+          <t>69492</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>103921</t>
+          <t>104617</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -10283,12 +10283,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>79543</t>
+          <t>79833</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>125887</t>
+          <t>126481</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>57974</t>
+          <t>59694</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>89405</t>
+          <t>91305</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10333,12 +10333,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>149751</t>
+          <t>148502</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>208466</t>
+          <t>206361</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19E-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19E-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>182800</t>
+          <t>182543</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>225070</t>
+          <t>225192</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>188846</t>
+          <t>189205</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>227364</t>
+          <t>226052</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>386507</t>
+          <t>385991</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>445102</t>
+          <t>442389</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,68%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94545</t>
+          <t>94069</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131716</t>
+          <t>131633</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71593</t>
+          <t>71763</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>105357</t>
+          <t>107539</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>175204</t>
+          <t>177656</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>226176</t>
+          <t>224289</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,24%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70482</t>
+          <t>70113</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106412</t>
+          <t>105762</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33010</t>
+          <t>31831</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57060</t>
+          <t>55963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>108795</t>
+          <t>110910</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>153854</t>
+          <t>151878</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19281</t>
+          <t>19912</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5669</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21376</t>
+          <t>20797</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15499</t>
+          <t>14815</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20365</t>
+          <t>21575</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>143053</t>
+          <t>144199</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>181998</t>
+          <t>182319</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>162685</t>
+          <t>165308</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>201327</t>
+          <t>202827</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>318561</t>
+          <t>322003</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>374552</t>
+          <t>377347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,38%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98753</t>
+          <t>95458</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134126</t>
+          <t>131492</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>106179</t>
+          <t>106046</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142459</t>
+          <t>143748</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>215612</t>
+          <t>213378</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>269500</t>
+          <t>264684</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,04%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54546</t>
+          <t>52762</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>85305</t>
+          <t>83044</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43116</t>
+          <t>41588</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72372</t>
+          <t>72496</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>103483</t>
+          <t>103864</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>145840</t>
+          <t>146014</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11809</t>
+          <t>13048</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10466</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18086</t>
+          <t>18715</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8434</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24501</t>
+          <t>24031</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25161</t>
+          <t>25695</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>151559</t>
+          <t>151806</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>194710</t>
+          <t>195298</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67507</t>
+          <t>67541</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94417</t>
+          <t>94802</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>229395</t>
+          <t>229257</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>281887</t>
+          <t>279644</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,58%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>136622</t>
+          <t>137347</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>179670</t>
+          <t>179056</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38964</t>
+          <t>38569</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62160</t>
+          <t>63932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>182774</t>
+          <t>183925</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>232232</t>
+          <t>234130</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>113557</t>
+          <t>113396</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>154056</t>
+          <t>152843</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16195</t>
+          <t>15870</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35197</t>
+          <t>35288</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>134154</t>
+          <t>134064</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>178895</t>
+          <t>178337</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17021</t>
+          <t>16727</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10118</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22216</t>
+          <t>22499</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28093</t>
+          <t>27556</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52724</t>
+          <t>53497</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12114</t>
+          <t>11994</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29586</t>
+          <t>29953</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55480</t>
+          <t>55865</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>313069</t>
+          <t>315810</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>374560</t>
+          <t>375493</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>318625</t>
+          <t>321534</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>379363</t>
+          <t>377459</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>651035</t>
+          <t>649287</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>737554</t>
+          <t>733293</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,22%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>299467</t>
+          <t>300549</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>359287</t>
+          <t>360251</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>269102</t>
+          <t>271983</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>327923</t>
+          <t>327323</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>587505</t>
+          <t>590553</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>667828</t>
+          <t>674162</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>269159</t>
+          <t>267777</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>329380</t>
+          <t>326858</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>112018</t>
+          <t>114520</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155929</t>
+          <t>156060</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>397919</t>
+          <t>396640</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>470379</t>
+          <t>470018</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25692</t>
+          <t>27962</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51111</t>
+          <t>52640</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19555</t>
+          <t>19344</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34669</t>
+          <t>34822</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>65153</t>
+          <t>63391</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>85404</t>
+          <t>84041</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>123754</t>
+          <t>123677</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23480</t>
+          <t>24626</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>95599</t>
+          <t>97359</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>138750</t>
+          <t>139747</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>134072</t>
+          <t>135318</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>176432</t>
+          <t>180127</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>233009</t>
+          <t>231531</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>285677</t>
+          <t>287810</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>380866</t>
+          <t>379317</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>450167</t>
+          <t>447154</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,83%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>160672</t>
+          <t>156634</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>204823</t>
+          <t>203411</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>221176</t>
+          <t>220494</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>271352</t>
+          <t>273572</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>391591</t>
+          <t>396444</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>461919</t>
+          <t>465479</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>138780</t>
+          <t>134814</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>181134</t>
+          <t>177414</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>142515</t>
+          <t>143667</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>189271</t>
+          <t>189624</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>292116</t>
+          <t>296576</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>354464</t>
+          <t>357562</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20150</t>
+          <t>20560</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>42339</t>
+          <t>43179</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7334</t>
+          <t>7272</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>23099</t>
+          <t>21288</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>31624</t>
+          <t>32049</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>56695</t>
+          <t>57214</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>59476</t>
+          <t>60343</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>92908</t>
+          <t>91627</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>27325</t>
+          <t>27010</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51135</t>
+          <t>52657</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>94368</t>
+          <t>95593</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>135493</t>
+          <t>135572</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>99629</t>
+          <t>98738</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>131628</t>
+          <t>133888</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>376151</t>
+          <t>377102</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>440621</t>
+          <t>441042</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>487653</t>
+          <t>486291</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>561241</t>
+          <t>561594</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,54%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>79278</t>
+          <t>78242</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>110562</t>
+          <t>111822</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>289643</t>
+          <t>288055</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>350283</t>
+          <t>350837</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>381610</t>
+          <t>379555</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>450958</t>
+          <t>449046</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>48816</t>
+          <t>48836</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>77058</t>
+          <t>77892</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>187484</t>
+          <t>187936</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>243809</t>
+          <t>240849</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>246471</t>
+          <t>247279</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>307119</t>
+          <t>308054</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>10703</t>
+          <t>11177</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>22356</t>
+          <t>22168</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>47020</t>
+          <t>46001</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>26475</t>
+          <t>27626</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>51695</t>
+          <t>53564</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>948</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>48129</t>
+          <t>49743</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>83382</t>
+          <t>80349</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>50965</t>
+          <t>50119</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>83887</t>
+          <t>83004</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1093801</t>
+          <t>1098868</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1211987</t>
+          <t>1211352</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1430088</t>
+          <t>1434177</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1548114</t>
+          <t>1550567</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2566187</t>
+          <t>2563243</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2728875</t>
+          <t>2722285</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,42%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>936230</t>
+          <t>936855</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1041700</t>
+          <t>1051962</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1071914</t>
+          <t>1070773</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1187456</t>
+          <t>1180678</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2043988</t>
+          <t>2042241</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2199923</t>
+          <t>2201909</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,7%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>754543</t>
+          <t>757553</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>860129</t>
+          <t>852080</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>589397</t>
+          <t>592655</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>684090</t>
+          <t>688354</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1376292</t>
+          <t>1375895</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1506111</t>
+          <t>1509157</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>81039</t>
+          <t>79388</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>120515</t>
+          <t>120403</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>48038</t>
+          <t>47536</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>83103</t>
+          <t>80863</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>138411</t>
+          <t>137650</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>190152</t>
+          <t>189714</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>211167</t>
+          <t>213937</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>275175</t>
+          <t>273691</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>102842</t>
+          <t>102279</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>147709</t>
+          <t>145133</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>328371</t>
+          <t>331156</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>404033</t>
+          <t>402021</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -5734,32 +5734,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>145866</t>
+          <t>168562</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>126621</t>
+          <t>146511</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>167065</t>
+          <t>191332</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5769,32 +5769,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>203114</t>
+          <t>220025</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>184733</t>
+          <t>201524</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>221130</t>
+          <t>238405</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5804,32 +5804,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>348980</t>
+          <t>388587</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>319997</t>
+          <t>359995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>377176</t>
+          <t>418983</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>40,37%</t>
         </is>
       </c>
     </row>
@@ -5847,32 +5847,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>276643</t>
+          <t>291816</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>252061</t>
+          <t>268120</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>297559</t>
+          <t>317687</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5882,32 +5882,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>205853</t>
+          <t>226499</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>188630</t>
+          <t>206236</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>224319</t>
+          <t>244384</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5917,32 +5917,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>482496</t>
+          <t>518315</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>452805</t>
+          <t>488274</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>511632</t>
+          <t>553895</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,38%</t>
         </is>
       </c>
     </row>
@@ -5960,32 +5960,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>78437</t>
+          <t>85781</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64141</t>
+          <t>69861</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100520</t>
+          <t>104683</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5995,32 +5995,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33190</t>
+          <t>36384</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24954</t>
+          <t>26737</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46334</t>
+          <t>49034</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6030,32 +6030,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>111628</t>
+          <t>122165</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>93306</t>
+          <t>102451</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>132969</t>
+          <t>144906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>6253</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6108,22 +6108,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>613</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6143,32 +6143,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>8957</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6221,67 +6221,67 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>6826</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>4444</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>4283</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1659</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>9686</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -6299,17 +6299,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>504474</t>
+          <t>549892</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>504474</t>
+          <t>549892</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>504474</t>
+          <t>549892</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6334,17 +6334,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>446903</t>
+          <t>487839</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>446903</t>
+          <t>487839</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>446903</t>
+          <t>487839</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6369,17 +6369,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>951377</t>
+          <t>1037730</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>951377</t>
+          <t>1037730</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>951377</t>
+          <t>1037730</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6416,32 +6416,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>122004</t>
+          <t>131804</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102821</t>
+          <t>112308</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>141880</t>
+          <t>153752</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6451,32 +6451,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>150779</t>
+          <t>167826</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>135290</t>
+          <t>149391</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>167243</t>
+          <t>184236</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6486,32 +6486,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>272783</t>
+          <t>299630</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>246687</t>
+          <t>276369</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>300029</t>
+          <t>327885</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -6529,32 +6529,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>231790</t>
+          <t>251549</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>208158</t>
+          <t>228616</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>253254</t>
+          <t>273682</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6564,32 +6564,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>189004</t>
+          <t>209360</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>173807</t>
+          <t>192494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>206132</t>
+          <t>227944</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6599,32 +6599,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>420795</t>
+          <t>460909</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>393433</t>
+          <t>430061</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>447636</t>
+          <t>487399</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,85%</t>
         </is>
       </c>
     </row>
@@ -6642,32 +6642,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>84302</t>
+          <t>84938</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>67025</t>
+          <t>69287</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>101941</t>
+          <t>105355</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6677,32 +6677,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>39380</t>
+          <t>42393</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30695</t>
+          <t>32989</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50153</t>
+          <t>54658</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6712,32 +6712,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>123682</t>
+          <t>127332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>103882</t>
+          <t>108724</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>144979</t>
+          <t>149682</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -6755,17 +6755,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1620</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11084</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6825,32 +6825,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>6386</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2328</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12654</t>
+          <t>12668</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -6868,32 +6868,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8684</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16527</t>
+          <t>17173</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6903,32 +6903,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>596</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6938,32 +6938,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>10468</t>
+          <t>10898</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18839</t>
+          <t>19054</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -6981,17 +6981,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>451660</t>
+          <t>482536</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>451660</t>
+          <t>482536</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>451660</t>
+          <t>482536</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7016,17 +7016,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>382085</t>
+          <t>422618</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>382085</t>
+          <t>422618</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>382085</t>
+          <t>422618</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7051,17 +7051,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>833745</t>
+          <t>905154</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>833745</t>
+          <t>905154</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>833745</t>
+          <t>905154</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7098,32 +7098,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>321688</t>
+          <t>96792</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>114962</t>
+          <t>79981</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>529590</t>
+          <t>115005</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7133,32 +7133,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>49383</t>
+          <t>57958</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40400</t>
+          <t>47576</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59975</t>
+          <t>70436</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7168,32 +7168,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>371071</t>
+          <t>154750</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>170252</t>
+          <t>132153</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>631511</t>
+          <t>176888</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -7211,32 +7211,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>220919</t>
+          <t>241488</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85917</t>
+          <t>216392</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>360216</t>
+          <t>262865</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7246,32 +7246,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>92246</t>
+          <t>102557</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>82188</t>
+          <t>90467</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101777</t>
+          <t>113331</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7281,32 +7281,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>313165</t>
+          <t>344045</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>136602</t>
+          <t>321776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>453319</t>
+          <t>367813</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>56,2%</t>
         </is>
       </c>
     </row>
@@ -7324,32 +7324,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>96992</t>
+          <t>104354</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36863</t>
+          <t>87935</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>160226</t>
+          <t>124116</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7359,32 +7359,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21375</t>
+          <t>22323</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15640</t>
+          <t>16616</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28735</t>
+          <t>30070</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7394,32 +7394,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>118367</t>
+          <t>126676</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49391</t>
+          <t>107798</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>178426</t>
+          <t>146905</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>22,45%</t>
         </is>
       </c>
     </row>
@@ -7437,67 +7437,67 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6219</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>12956</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1447</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4329</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1353</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3940</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7507,32 +7507,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>8014</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>4144</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13661</t>
+          <t>14010</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -7550,32 +7550,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>19144</t>
+          <t>19061</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>11452</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34075</t>
+          <t>28757</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7585,32 +7585,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>541</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7620,32 +7620,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>20969</t>
+          <t>20945</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>13712</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36128</t>
+          <t>30463</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -7663,17 +7663,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>664962</t>
+          <t>468262</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>664962</t>
+          <t>468262</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>664962</t>
+          <t>468262</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7698,17 +7698,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>166183</t>
+          <t>186168</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>166183</t>
+          <t>186168</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>166183</t>
+          <t>186168</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7733,17 +7733,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>831145</t>
+          <t>654430</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>831145</t>
+          <t>654430</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>831145</t>
+          <t>654430</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7780,32 +7780,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>191362</t>
+          <t>220461</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>163196</t>
+          <t>192474</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>218076</t>
+          <t>255293</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7815,32 +7815,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>244219</t>
+          <t>272447</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121759</t>
+          <t>246337</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>317486</t>
+          <t>297012</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7850,32 +7850,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>435581</t>
+          <t>492908</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>294902</t>
+          <t>453307</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>497748</t>
+          <t>532801</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -7893,102 +7893,102 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>512659</t>
+          <t>566372</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>473227</t>
+          <t>530525</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>547982</t>
+          <t>601188</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
+          <t>50,44%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>47,25%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>53,54%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>467498</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>441673</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>491560</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>54,34%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>51,34%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>57,14%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1033870</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>989411</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1076848</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>52,13%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>49,89%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>46,06%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>53,33%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>628297</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>527515</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>792385</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>64,29%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>53,98%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>81,08%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1235</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1140956</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1029094</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1444891</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>56,91%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>51,33%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>54,3%</t>
         </is>
       </c>
     </row>
@@ -8006,32 +8006,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>261280</t>
+          <t>270314</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>230212</t>
+          <t>239072</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>294112</t>
+          <t>298512</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8041,32 +8041,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>86797</t>
+          <t>101217</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>43075</t>
+          <t>85765</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>113788</t>
+          <t>118256</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8076,32 +8076,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>348077</t>
+          <t>371531</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>245489</t>
+          <t>339633</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>406518</t>
+          <t>407150</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -8119,32 +8119,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>19061</t>
+          <t>22502</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12215</t>
+          <t>14313</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27781</t>
+          <t>33390</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8154,32 +8154,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>7259</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2426</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12535</t>
+          <t>13462</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8189,32 +8189,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>25611</t>
+          <t>29761</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15535</t>
+          <t>20986</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36533</t>
+          <t>41740</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -8232,32 +8232,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>43116</t>
+          <t>43248</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31417</t>
+          <t>31296</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>58172</t>
+          <t>57847</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8267,32 +8267,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>11378</t>
+          <t>11873</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5028</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18624</t>
+          <t>18741</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8302,32 +8302,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>54494</t>
+          <t>55121</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>37034</t>
+          <t>42285</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>72502</t>
+          <t>69980</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -8345,17 +8345,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1027478</t>
+          <t>1122898</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1027478</t>
+          <t>1122898</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1027478</t>
+          <t>1122898</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8380,17 +8380,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>977240</t>
+          <t>860293</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>977240</t>
+          <t>860293</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>977240</t>
+          <t>860293</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8415,17 +8415,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2004718</t>
+          <t>1983190</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2004718</t>
+          <t>1983190</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2004718</t>
+          <t>1983190</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8462,32 +8462,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>80591</t>
+          <t>94632</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>63923</t>
+          <t>73817</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>105729</t>
+          <t>118083</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8497,32 +8497,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>207694</t>
+          <t>197933</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>159780</t>
+          <t>176589</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>280298</t>
+          <t>219123</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8532,32 +8532,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>288285</t>
+          <t>292564</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>238863</t>
+          <t>262436</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>372867</t>
+          <t>323775</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -8575,32 +8575,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>224052</t>
+          <t>272363</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>203012</t>
+          <t>245139</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>247423</t>
+          <t>299903</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8610,32 +8610,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>441225</t>
+          <t>427568</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>386239</t>
+          <t>403386</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>537595</t>
+          <t>451134</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8645,32 +8645,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>665277</t>
+          <t>699930</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>610949</t>
+          <t>664610</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>770088</t>
+          <t>735332</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>52,9%</t>
         </is>
       </c>
     </row>
@@ -8688,32 +8688,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>123450</t>
+          <t>148446</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>106168</t>
+          <t>128307</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>143682</t>
+          <t>171941</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8723,32 +8723,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>144291</t>
+          <t>155126</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>105428</t>
+          <t>137523</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>168498</t>
+          <t>173946</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8758,32 +8758,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>267741</t>
+          <t>303572</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>220995</t>
+          <t>275189</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>297634</t>
+          <t>330195</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -8801,32 +8801,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>14376</t>
+          <t>14791</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21773</t>
+          <t>22374</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8836,32 +8836,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>14476</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>11455</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21723</t>
+          <t>25044</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8871,32 +8871,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>28852</t>
+          <t>31561</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>20687</t>
+          <t>21783</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>39704</t>
+          <t>41605</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -8914,102 +8914,102 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>30146</t>
+          <t>33793</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>21220</t>
+          <t>23813</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>41723</t>
+          <t>45219</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
+          <t>4,22%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>28575</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>21324</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>36832</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>62368</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>50394</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>75618</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
           <t>4,49%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>27904</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>19502</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>37700</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>58050</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>44032</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>72071</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -9027,17 +9027,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>472616</t>
+          <t>564024</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>472616</t>
+          <t>564024</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>472616</t>
+          <t>564024</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -9062,17 +9062,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>835590</t>
+          <t>825973</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>835590</t>
+          <t>825973</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>835590</t>
+          <t>825973</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -9097,17 +9097,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1308206</t>
+          <t>1389996</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1308206</t>
+          <t>1389996</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1308206</t>
+          <t>1389996</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -9129,7 +9129,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9144,32 +9144,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>76224</t>
+          <t>80349</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>55221</t>
+          <t>57411</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>103708</t>
+          <t>106273</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9179,32 +9179,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>208468</t>
+          <t>226744</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>184859</t>
+          <t>202293</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>235320</t>
+          <t>252780</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9214,32 +9214,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>284692</t>
+          <t>307092</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>251186</t>
+          <t>273339</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>324630</t>
+          <t>341836</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -9257,32 +9257,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>145321</t>
+          <t>137763</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>118353</t>
+          <t>111503</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>168715</t>
+          <t>161224</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9292,32 +9292,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>384702</t>
+          <t>428596</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>358181</t>
+          <t>400148</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>408752</t>
+          <t>457566</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9327,32 +9327,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>530023</t>
+          <t>566359</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>491416</t>
+          <t>532294</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>567366</t>
+          <t>604965</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>56,64%</t>
         </is>
       </c>
     </row>
@@ -9370,32 +9370,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>16225</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>31069</t>
+          <t>29355</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9405,32 +9405,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>115561</t>
+          <t>131560</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>100387</t>
+          <t>114803</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>131734</t>
+          <t>149629</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9440,32 +9440,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>131786</t>
+          <t>146576</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>114528</t>
+          <t>126815</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>153780</t>
+          <t>168517</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -9483,7 +9483,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>925</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9518,32 +9518,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>13974</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>19088</t>
+          <t>21562</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9553,32 +9553,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>13022</t>
+          <t>14899</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>8254</t>
+          <t>9496</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>19935</t>
+          <t>22780</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -9596,32 +9596,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>716</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9631,32 +9631,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>28743</t>
+          <t>30053</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>21324</t>
+          <t>22030</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>39322</t>
+          <t>39824</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9666,32 +9666,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>30485</t>
+          <t>33228</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>22265</t>
+          <t>25234</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>40144</t>
+          <t>43381</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -9709,17 +9709,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9744,17 +9744,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>749500</t>
+          <t>830927</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>749500</t>
+          <t>830927</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>749500</t>
+          <t>830927</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9779,17 +9779,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>990008</t>
+          <t>1068155</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>990008</t>
+          <t>1068155</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>990008</t>
+          <t>1068155</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9826,32 +9826,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>937735</t>
+          <t>792599</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>733173</t>
+          <t>735272</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1471231</t>
+          <t>852057</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9861,32 +9861,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1063656</t>
+          <t>1142933</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>858646</t>
+          <t>1094280</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1165970</t>
+          <t>1200186</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9896,32 +9896,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>2001391</t>
+          <t>1935532</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1779486</t>
+          <t>1862414</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2640085</t>
+          <t>2009124</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -9939,32 +9939,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1611386</t>
+          <t>1761351</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1249728</t>
+          <t>1691333</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1757217</t>
+          <t>1825256</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9974,32 +9974,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1941326</t>
+          <t>1862078</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1805738</t>
+          <t>1810239</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2256375</t>
+          <t>1917404</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10009,32 +10009,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>3552712</t>
+          <t>3623429</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3158911</t>
+          <t>3525998</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3815954</t>
+          <t>3700299</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>52,57%</t>
         </is>
       </c>
     </row>
@@ -10052,32 +10052,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>660687</t>
+          <t>708849</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>507819</t>
+          <t>659149</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>733565</t>
+          <t>761354</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10087,32 +10087,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>440594</t>
+          <t>489003</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>350933</t>
+          <t>455642</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>486873</t>
+          <t>524022</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10122,32 +10122,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1101281</t>
+          <t>1197852</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>958621</t>
+          <t>1134522</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1196554</t>
+          <t>1256724</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -10165,32 +10165,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>47343</t>
+          <t>51905</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>35170</t>
+          <t>40459</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>62002</t>
+          <t>68667</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10200,32 +10200,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>37721</t>
+          <t>42935</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>28547</t>
+          <t>33259</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>50391</t>
+          <t>54493</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10235,32 +10235,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>85065</t>
+          <t>94840</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>69492</t>
+          <t>79901</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>104617</t>
+          <t>116465</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -10278,32 +10278,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>104547</t>
+          <t>110135</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>79833</t>
+          <t>91141</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>126481</t>
+          <t>131172</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10313,32 +10313,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>74202</t>
+          <t>76868</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>59694</t>
+          <t>64356</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>91305</t>
+          <t>92321</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>178750</t>
+          <t>187002</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>148502</t>
+          <t>165532</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>206361</t>
+          <t>213992</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -10391,17 +10391,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3361698</t>
+          <t>3424839</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3361698</t>
+          <t>3424839</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3361698</t>
+          <t>3424839</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10426,17 +10426,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3557500</t>
+          <t>3613817</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3557500</t>
+          <t>3613817</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3557500</t>
+          <t>3613817</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10461,17 +10461,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>6919198</t>
+          <t>7038656</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6919198</t>
+          <t>7038656</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6919198</t>
+          <t>7038656</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
